--- a/others/data_n_rules.xlsx
+++ b/others/data_n_rules.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\@DOKUMEN\KULIAH\1. Semesteran\Smt 7\2. Sistem Pakar\Project-Sistem-Pakar-Optimasi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\@DOKUMEN\KULIAH\1. Semesteran\Smt 7\2. Sistem Pakar\Project-Sistem-Pakar-Optimasi\others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7225D497-E781-4320-B894-ADCD56725270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25D6DA0-AC36-4D28-8E65-837A58168E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rules" sheetId="3" r:id="rId1"/>
